--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1804,6 +1804,1380 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123234392</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>585531</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7041481</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123236138</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91243</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>585273</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7041240</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123232328</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>585493</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7041342</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123235320</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>585455</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7041321</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123233683</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>585497</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7041338</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, torrgran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123231973</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585476</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7041349</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123231596</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>585465</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7041291</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123232752</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>585409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7041371</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123232462</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>585466</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7041382</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123232716</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>585414</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7041365</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123233556</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90948</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>585476</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7041386</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123235375</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>585426</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7041283</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123234354</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>585533</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7041481</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3178,6 +3178,108 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123236358</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91301</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>585276</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7041255</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -2976,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123235375</v>
+        <v>123234354</v>
       </c>
       <c r="B24" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585426</v>
+        <v>585533</v>
       </c>
       <c r="R24" t="n">
-        <v>7041283</v>
+        <v>7041481</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123234354</v>
+        <v>123235375</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3094,21 +3094,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585533</v>
+        <v>585426</v>
       </c>
       <c r="R25" t="n">
-        <v>7041481</v>
+        <v>7041283</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123234392</v>
+        <v>123236138</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>91243</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585531</v>
+        <v>585273</v>
       </c>
       <c r="R13" t="n">
-        <v>7041481</v>
+        <v>7041240</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123236138</v>
+        <v>123232462</v>
       </c>
       <c r="B14" t="n">
-        <v>91243</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,38 +1920,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585273</v>
+        <v>585466</v>
       </c>
       <c r="R14" t="n">
-        <v>7041240</v>
+        <v>7041382</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123232328</v>
+        <v>123235375</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,42 +2026,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585493</v>
+        <v>585426</v>
       </c>
       <c r="R15" t="n">
-        <v>7041342</v>
+        <v>7041283</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2090,11 +2090,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2121,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123235320</v>
+        <v>123231973</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,16 +2132,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2157,7 +2152,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2166,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585455</v>
+        <v>585476</v>
       </c>
       <c r="R16" t="n">
-        <v>7041321</v>
+        <v>7041349</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2202,6 +2197,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2228,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123233683</v>
+        <v>123234392</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2244,39 +2244,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585497</v>
+        <v>585531</v>
       </c>
       <c r="R17" t="n">
-        <v>7041338</v>
+        <v>7041481</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2309,11 +2304,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,7 +2330,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123231973</v>
+        <v>123233683</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2385,10 +2375,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585476</v>
+        <v>585497</v>
       </c>
       <c r="R18" t="n">
-        <v>7041349</v>
+        <v>7041338</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2425,7 +2415,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2452,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123231596</v>
+        <v>123234354</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2468,39 +2458,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585465</v>
+        <v>585533</v>
       </c>
       <c r="R19" t="n">
-        <v>7041291</v>
+        <v>7041481</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2533,11 +2518,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2564,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123232752</v>
+        <v>123233556</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>90948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,21 +2560,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2604,10 +2584,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585409</v>
+        <v>585476</v>
       </c>
       <c r="R20" t="n">
-        <v>7041371</v>
+        <v>7041386</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2666,10 +2646,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123232462</v>
+        <v>123235320</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2678,30 +2658,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2710,10 +2691,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585466</v>
+        <v>585455</v>
       </c>
       <c r="R21" t="n">
-        <v>7041382</v>
+        <v>7041321</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2772,10 +2753,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123232716</v>
+        <v>123232328</v>
       </c>
       <c r="B22" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2784,38 +2765,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585414</v>
+        <v>585493</v>
       </c>
       <c r="R22" t="n">
-        <v>7041365</v>
+        <v>7041342</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2848,6 +2833,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2874,10 +2864,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123233556</v>
+        <v>123232716</v>
       </c>
       <c r="B23" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,21 +2880,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2914,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585476</v>
+        <v>585414</v>
       </c>
       <c r="R23" t="n">
-        <v>7041386</v>
+        <v>7041365</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2976,7 +2966,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123234354</v>
+        <v>123232752</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3016,10 +3006,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585533</v>
+        <v>585409</v>
       </c>
       <c r="R24" t="n">
-        <v>7041481</v>
+        <v>7041371</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3078,10 +3068,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123235375</v>
+        <v>123231596</v>
       </c>
       <c r="B25" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3094,34 +3084,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585426</v>
+        <v>585465</v>
       </c>
       <c r="R25" t="n">
-        <v>7041283</v>
+        <v>7041291</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3154,6 +3149,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123236138</v>
+        <v>123232716</v>
       </c>
       <c r="B13" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585273</v>
+        <v>585414</v>
       </c>
       <c r="R13" t="n">
-        <v>7041240</v>
+        <v>7041365</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123235375</v>
+        <v>123232328</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,38 +2026,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585426</v>
+        <v>585493</v>
       </c>
       <c r="R15" t="n">
-        <v>7041283</v>
+        <v>7041342</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2090,6 +2094,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,10 +2125,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123231973</v>
+        <v>123232752</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2132,39 +2141,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585476</v>
+        <v>585409</v>
       </c>
       <c r="R16" t="n">
-        <v>7041349</v>
+        <v>7041371</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2197,11 +2201,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2228,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123234392</v>
+        <v>123234354</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2244,21 +2243,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,7 +2267,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585531</v>
+        <v>585533</v>
       </c>
       <c r="R17" t="n">
         <v>7041481</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123233683</v>
+        <v>123235375</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,39 +2345,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585497</v>
+        <v>585426</v>
       </c>
       <c r="R18" t="n">
-        <v>7041338</v>
+        <v>7041283</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2411,11 +2405,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2442,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123234354</v>
+        <v>123233683</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,34 +2447,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585533</v>
+        <v>585497</v>
       </c>
       <c r="R19" t="n">
-        <v>7041481</v>
+        <v>7041338</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2518,6 +2512,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123233556</v>
+        <v>123235320</v>
       </c>
       <c r="B20" t="n">
-        <v>90948</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2560,34 +2559,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585476</v>
+        <v>585455</v>
       </c>
       <c r="R20" t="n">
-        <v>7041386</v>
+        <v>7041321</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2646,10 +2650,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123235320</v>
+        <v>123236138</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>91243</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2662,39 +2666,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585455</v>
+        <v>585273</v>
       </c>
       <c r="R21" t="n">
-        <v>7041321</v>
+        <v>7041240</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2753,10 +2752,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123232328</v>
+        <v>123233556</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>90948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2765,42 +2764,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585493</v>
+        <v>585476</v>
       </c>
       <c r="R22" t="n">
-        <v>7041342</v>
+        <v>7041386</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2833,11 +2828,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,10 +2854,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123232716</v>
+        <v>123231596</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,34 +2870,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585414</v>
+        <v>585465</v>
       </c>
       <c r="R23" t="n">
-        <v>7041365</v>
+        <v>7041291</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2940,6 +2935,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123232752</v>
+        <v>123234392</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,21 +2982,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585409</v>
+        <v>585531</v>
       </c>
       <c r="R24" t="n">
-        <v>7041371</v>
+        <v>7041481</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123231596</v>
+        <v>123231973</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585465</v>
+        <v>585476</v>
       </c>
       <c r="R25" t="n">
-        <v>7041291</v>
+        <v>7041349</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123234392</v>
+        <v>123231973</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,34 +2982,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585531</v>
+        <v>585476</v>
       </c>
       <c r="R24" t="n">
-        <v>7041481</v>
+        <v>7041349</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3042,6 +3047,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3068,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123231973</v>
+        <v>123234392</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,39 +3094,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585476</v>
+        <v>585531</v>
       </c>
       <c r="R25" t="n">
-        <v>7041349</v>
+        <v>7041481</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3149,11 +3154,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1809,7 +1809,7 @@
         <v>123232716</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123232462</v>
+        <v>123233683</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,30 +1920,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1952,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585466</v>
+        <v>585497</v>
       </c>
       <c r="R14" t="n">
-        <v>7041382</v>
+        <v>7041338</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1988,6 +1989,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123232328</v>
+        <v>123231973</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,30 +2032,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2058,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585493</v>
+        <v>585476</v>
       </c>
       <c r="R15" t="n">
-        <v>7041342</v>
+        <v>7041349</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2098,7 +2105,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Delvis snötäckt mark</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2125,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123232752</v>
+        <v>123232462</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,38 +2144,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585409</v>
+        <v>585466</v>
       </c>
       <c r="R16" t="n">
-        <v>7041371</v>
+        <v>7041382</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2227,10 +2238,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123234354</v>
+        <v>123232752</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2267,10 +2278,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585533</v>
+        <v>585409</v>
       </c>
       <c r="R17" t="n">
-        <v>7041481</v>
+        <v>7041371</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2329,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123235375</v>
+        <v>123232328</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2341,38 +2352,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585426</v>
+        <v>585493</v>
       </c>
       <c r="R18" t="n">
-        <v>7041283</v>
+        <v>7041342</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2405,6 +2420,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123233683</v>
+        <v>123234392</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,39 +2467,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585497</v>
+        <v>585531</v>
       </c>
       <c r="R19" t="n">
-        <v>7041338</v>
+        <v>7041481</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2512,11 +2527,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123235320</v>
+        <v>123233556</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>90951</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2559,39 +2569,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585455</v>
+        <v>585476</v>
       </c>
       <c r="R20" t="n">
-        <v>7041321</v>
+        <v>7041386</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2650,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123236138</v>
+        <v>123231596</v>
       </c>
       <c r="B21" t="n">
-        <v>91243</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2666,34 +2671,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585273</v>
+        <v>585465</v>
       </c>
       <c r="R21" t="n">
-        <v>7041240</v>
+        <v>7041291</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,6 +2736,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2752,10 +2767,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123233556</v>
+        <v>123236138</v>
       </c>
       <c r="B22" t="n">
-        <v>90948</v>
+        <v>91242</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2768,21 +2783,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2792,10 +2807,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585476</v>
+        <v>585273</v>
       </c>
       <c r="R22" t="n">
-        <v>7041386</v>
+        <v>7041240</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2854,10 +2869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123231596</v>
+        <v>123235320</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2870,16 +2885,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2890,7 +2905,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2899,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585465</v>
+        <v>585455</v>
       </c>
       <c r="R23" t="n">
-        <v>7041291</v>
+        <v>7041321</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2935,11 +2950,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2966,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123231973</v>
+        <v>123234354</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,39 +2992,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585476</v>
+        <v>585533</v>
       </c>
       <c r="R24" t="n">
-        <v>7041349</v>
+        <v>7041481</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3047,11 +3052,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3078,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123234392</v>
+        <v>123235375</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3094,21 +3094,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585531</v>
+        <v>585426</v>
       </c>
       <c r="R25" t="n">
-        <v>7041481</v>
+        <v>7041283</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3183,7 +3183,7 @@
         <v>123236358</v>
       </c>
       <c r="B26" t="n">
-        <v>91301</v>
+        <v>91304</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123232716</v>
+        <v>123235375</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585414</v>
+        <v>585426</v>
       </c>
       <c r="R13" t="n">
-        <v>7041365</v>
+        <v>7041283</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,7 +1908,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123233683</v>
+        <v>123231596</v>
       </c>
       <c r="B14" t="n">
         <v>57481</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585497</v>
+        <v>585465</v>
       </c>
       <c r="R14" t="n">
-        <v>7041338</v>
+        <v>7041291</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack, torrgran</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123231973</v>
+        <v>123234354</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,39 +2036,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585476</v>
+        <v>585533</v>
       </c>
       <c r="R15" t="n">
-        <v>7041349</v>
+        <v>7041481</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,11 +2096,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123232462</v>
+        <v>123232752</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,42 +2134,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585466</v>
+        <v>585409</v>
       </c>
       <c r="R16" t="n">
-        <v>7041382</v>
+        <v>7041371</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2238,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123232752</v>
+        <v>123235320</v>
       </c>
       <c r="B17" t="n">
-        <v>79850</v>
+        <v>57497</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2254,34 +2240,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585409</v>
+        <v>585455</v>
       </c>
       <c r="R17" t="n">
-        <v>7041371</v>
+        <v>7041321</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2340,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123232328</v>
+        <v>123232716</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>90957</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,42 +2343,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585493</v>
+        <v>585414</v>
       </c>
       <c r="R18" t="n">
-        <v>7041342</v>
+        <v>7041365</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2420,11 +2407,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2451,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123234392</v>
+        <v>123236138</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>91244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585531</v>
+        <v>585273</v>
       </c>
       <c r="R19" t="n">
-        <v>7041481</v>
+        <v>7041240</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2553,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123233556</v>
+        <v>123234392</v>
       </c>
       <c r="B20" t="n">
-        <v>90951</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,21 +2551,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585476</v>
+        <v>585531</v>
       </c>
       <c r="R20" t="n">
-        <v>7041386</v>
+        <v>7041481</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2655,7 +2637,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123231596</v>
+        <v>123233683</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2700,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585465</v>
+        <v>585497</v>
       </c>
       <c r="R21" t="n">
-        <v>7041291</v>
+        <v>7041338</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2740,7 +2722,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2767,10 +2749,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123236138</v>
+        <v>123232462</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2779,38 +2761,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585273</v>
+        <v>585466</v>
       </c>
       <c r="R22" t="n">
-        <v>7041240</v>
+        <v>7041382</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2869,10 +2855,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123235320</v>
+        <v>123233556</v>
       </c>
       <c r="B23" t="n">
-        <v>57497</v>
+        <v>90953</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2885,39 +2871,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585455</v>
+        <v>585476</v>
       </c>
       <c r="R23" t="n">
-        <v>7041321</v>
+        <v>7041386</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2976,10 +2957,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123234354</v>
+        <v>123231973</v>
       </c>
       <c r="B24" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2992,34 +2973,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585533</v>
+        <v>585476</v>
       </c>
       <c r="R24" t="n">
-        <v>7041481</v>
+        <v>7041349</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3052,6 +3038,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3078,10 +3069,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123235375</v>
+        <v>123232328</v>
       </c>
       <c r="B25" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,38 +3081,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585426</v>
+        <v>585493</v>
       </c>
       <c r="R25" t="n">
-        <v>7041283</v>
+        <v>7041342</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3154,6 +3149,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3183,7 @@
         <v>123236358</v>
       </c>
       <c r="B26" t="n">
-        <v>91304</v>
+        <v>91306</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123231596</v>
+        <v>123234354</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,39 +1924,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585465</v>
+        <v>585533</v>
       </c>
       <c r="R14" t="n">
-        <v>7041291</v>
+        <v>7041481</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,11 +1984,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123234354</v>
+        <v>123231596</v>
       </c>
       <c r="B15" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,34 +2026,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585533</v>
+        <v>585465</v>
       </c>
       <c r="R15" t="n">
-        <v>7041481</v>
+        <v>7041291</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2096,6 +2091,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123235375</v>
+        <v>123231596</v>
       </c>
       <c r="B13" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,34 +1822,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585426</v>
+        <v>585465</v>
       </c>
       <c r="R13" t="n">
-        <v>7041283</v>
+        <v>7041291</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1882,6 +1887,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123234354</v>
+        <v>123235320</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>57497</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,34 +1934,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585533</v>
+        <v>585455</v>
       </c>
       <c r="R14" t="n">
-        <v>7041481</v>
+        <v>7041321</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123231596</v>
+        <v>123235375</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>90963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,39 +2041,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585465</v>
+        <v>585426</v>
       </c>
       <c r="R15" t="n">
-        <v>7041291</v>
+        <v>7041283</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2091,11 +2101,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123232752</v>
+        <v>123232462</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,38 +2139,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585409</v>
+        <v>585466</v>
       </c>
       <c r="R16" t="n">
-        <v>7041371</v>
+        <v>7041382</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2224,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235320</v>
+        <v>123233556</v>
       </c>
       <c r="B17" t="n">
-        <v>57497</v>
+        <v>90959</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,39 +2249,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585455</v>
+        <v>585476</v>
       </c>
       <c r="R17" t="n">
-        <v>7041321</v>
+        <v>7041386</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2334,7 +2338,7 @@
         <v>123232716</v>
       </c>
       <c r="B18" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236138</v>
+        <v>123233683</v>
       </c>
       <c r="B19" t="n">
-        <v>91244</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,34 +2453,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585273</v>
+        <v>585497</v>
       </c>
       <c r="R19" t="n">
-        <v>7041240</v>
+        <v>7041338</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2509,6 +2518,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2535,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123234392</v>
+        <v>123234354</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,21 +2565,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,7 +2589,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585531</v>
+        <v>585533</v>
       </c>
       <c r="R20" t="n">
         <v>7041481</v>
@@ -2637,10 +2651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123233683</v>
+        <v>123236138</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>91250</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,39 +2667,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585497</v>
+        <v>585273</v>
       </c>
       <c r="R21" t="n">
-        <v>7041338</v>
+        <v>7041240</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2718,11 +2727,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2749,10 +2753,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123232462</v>
+        <v>123232752</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>79853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,42 +2765,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585466</v>
+        <v>585409</v>
       </c>
       <c r="R22" t="n">
-        <v>7041382</v>
+        <v>7041371</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2855,10 +2855,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123233556</v>
+        <v>123234392</v>
       </c>
       <c r="B23" t="n">
-        <v>90953</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2871,21 +2871,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585476</v>
+        <v>585531</v>
       </c>
       <c r="R23" t="n">
-        <v>7041386</v>
+        <v>7041481</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3072,7 +3072,7 @@
         <v>123232328</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>123236358</v>
       </c>
       <c r="B26" t="n">
-        <v>91306</v>
+        <v>91312</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123235375</v>
+        <v>123232328</v>
       </c>
       <c r="B13" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,38 +1818,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585426</v>
+        <v>585493</v>
       </c>
       <c r="R13" t="n">
-        <v>7041283</v>
+        <v>7041342</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1882,6 +1886,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123232462</v>
+        <v>123234354</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>79862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,42 +1929,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585466</v>
+        <v>585533</v>
       </c>
       <c r="R14" t="n">
-        <v>7041382</v>
+        <v>7041481</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2014,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123232716</v>
+        <v>123232752</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>79862</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,21 +2035,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585414</v>
+        <v>585409</v>
       </c>
       <c r="R15" t="n">
-        <v>7041365</v>
+        <v>7041371</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123231596</v>
+        <v>123231973</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585465</v>
+        <v>585476</v>
       </c>
       <c r="R16" t="n">
-        <v>7041291</v>
+        <v>7041349</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2228,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123232328</v>
+        <v>123233683</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,30 +2245,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2272,10 +2278,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585493</v>
+        <v>585497</v>
       </c>
       <c r="R17" t="n">
-        <v>7041342</v>
+        <v>7041338</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2318,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Delvis snötäckt mark</t>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123233556</v>
+        <v>123235320</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>57503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,34 +2361,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585476</v>
+        <v>585455</v>
       </c>
       <c r="R18" t="n">
-        <v>7041386</v>
+        <v>7041321</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2441,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123231973</v>
+        <v>123236138</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>91270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,39 +2468,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585476</v>
+        <v>585273</v>
       </c>
       <c r="R19" t="n">
-        <v>7041349</v>
+        <v>7041240</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2522,11 +2528,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2553,10 +2554,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123232752</v>
+        <v>123232462</v>
       </c>
       <c r="B20" t="n">
-        <v>79856</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,38 +2566,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585409</v>
+        <v>585466</v>
       </c>
       <c r="R20" t="n">
-        <v>7041371</v>
+        <v>7041382</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2655,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123234354</v>
+        <v>123234392</v>
       </c>
       <c r="B21" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2695,7 +2700,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585533</v>
+        <v>585531</v>
       </c>
       <c r="R21" t="n">
         <v>7041481</v>
@@ -2757,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123235320</v>
+        <v>123231596</v>
       </c>
       <c r="B22" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,16 +2778,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2793,7 +2798,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2802,10 +2807,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585455</v>
+        <v>585465</v>
       </c>
       <c r="R22" t="n">
-        <v>7041321</v>
+        <v>7041291</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2838,6 +2843,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123236138</v>
+        <v>123233556</v>
       </c>
       <c r="B23" t="n">
-        <v>91253</v>
+        <v>90979</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,21 +2890,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585273</v>
+        <v>585476</v>
       </c>
       <c r="R23" t="n">
-        <v>7041240</v>
+        <v>7041386</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2966,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123234392</v>
+        <v>123235375</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,21 +2992,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3006,10 +3016,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585531</v>
+        <v>585426</v>
       </c>
       <c r="R24" t="n">
-        <v>7041481</v>
+        <v>7041283</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3068,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123233683</v>
+        <v>123232716</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>90983</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,39 +3094,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585497</v>
+        <v>585414</v>
       </c>
       <c r="R25" t="n">
-        <v>7041338</v>
+        <v>7041365</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3149,11 +3154,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3183,7 @@
         <v>123236358</v>
       </c>
       <c r="B26" t="n">
-        <v>91315</v>
+        <v>91332</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123234392</v>
+        <v>123233556</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
+        <v>90979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585531</v>
+        <v>585476</v>
       </c>
       <c r="R21" t="n">
-        <v>7041481</v>
+        <v>7041386</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123231596</v>
+        <v>123234392</v>
       </c>
       <c r="B22" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,39 +2778,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585465</v>
+        <v>585531</v>
       </c>
       <c r="R22" t="n">
-        <v>7041291</v>
+        <v>7041481</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2843,11 +2838,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2874,10 +2864,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123233556</v>
+        <v>123231596</v>
       </c>
       <c r="B23" t="n">
-        <v>90979</v>
+        <v>57487</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,34 +2880,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585476</v>
+        <v>585465</v>
       </c>
       <c r="R23" t="n">
-        <v>7041386</v>
+        <v>7041291</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2950,6 +2945,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123233556</v>
+        <v>123234392</v>
       </c>
       <c r="B21" t="n">
-        <v>90979</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585476</v>
+        <v>585531</v>
       </c>
       <c r="R21" t="n">
-        <v>7041386</v>
+        <v>7041481</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123234392</v>
+        <v>123231596</v>
       </c>
       <c r="B22" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,34 +2778,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585531</v>
+        <v>585465</v>
       </c>
       <c r="R22" t="n">
-        <v>7041481</v>
+        <v>7041291</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2838,6 +2843,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123231596</v>
+        <v>123233556</v>
       </c>
       <c r="B23" t="n">
-        <v>57487</v>
+        <v>90979</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,39 +2890,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585465</v>
+        <v>585476</v>
       </c>
       <c r="R23" t="n">
-        <v>7041291</v>
+        <v>7041386</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2945,11 +2950,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123232328</v>
+        <v>123233683</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,30 +1818,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1850,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585493</v>
+        <v>585497</v>
       </c>
       <c r="R13" t="n">
-        <v>7041342</v>
+        <v>7041338</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1890,7 +1891,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Delvis snötäckt mark</t>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,7 +1921,7 @@
         <v>123234354</v>
       </c>
       <c r="B14" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123232752</v>
+        <v>123235320</v>
       </c>
       <c r="B15" t="n">
-        <v>79862</v>
+        <v>57506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,34 +2036,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585409</v>
+        <v>585455</v>
       </c>
       <c r="R15" t="n">
-        <v>7041371</v>
+        <v>7041321</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2121,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123231973</v>
+        <v>123235375</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>90988</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2137,39 +2143,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585476</v>
+        <v>585426</v>
       </c>
       <c r="R16" t="n">
-        <v>7041349</v>
+        <v>7041283</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2202,11 +2203,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123233683</v>
+        <v>123232716</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>90988</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,39 +2245,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585497</v>
+        <v>585414</v>
       </c>
       <c r="R17" t="n">
-        <v>7041338</v>
+        <v>7041365</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2314,11 +2305,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2345,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123235320</v>
+        <v>123236138</v>
       </c>
       <c r="B18" t="n">
-        <v>57503</v>
+        <v>91275</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,39 +2347,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585455</v>
+        <v>585273</v>
       </c>
       <c r="R18" t="n">
-        <v>7041321</v>
+        <v>7041240</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236138</v>
+        <v>123231973</v>
       </c>
       <c r="B19" t="n">
-        <v>91270</v>
+        <v>57490</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2468,34 +2449,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585273</v>
+        <v>585476</v>
       </c>
       <c r="R19" t="n">
-        <v>7041240</v>
+        <v>7041349</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2528,6 +2514,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2554,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123232462</v>
+        <v>123232328</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,7 +2580,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2598,10 +2589,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585466</v>
+        <v>585493</v>
       </c>
       <c r="R20" t="n">
-        <v>7041382</v>
+        <v>7041342</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2634,6 +2625,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2660,10 +2656,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123234392</v>
+        <v>123233556</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
+        <v>90984</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2672,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585531</v>
+        <v>585476</v>
       </c>
       <c r="R21" t="n">
-        <v>7041481</v>
+        <v>7041386</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2762,10 +2758,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123231596</v>
+        <v>123232752</v>
       </c>
       <c r="B22" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,39 +2774,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585465</v>
+        <v>585409</v>
       </c>
       <c r="R22" t="n">
-        <v>7041291</v>
+        <v>7041371</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2843,11 +2834,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2874,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123233556</v>
+        <v>123234392</v>
       </c>
       <c r="B23" t="n">
-        <v>90979</v>
+        <v>78786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,21 +2876,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2914,10 +2900,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585476</v>
+        <v>585531</v>
       </c>
       <c r="R23" t="n">
-        <v>7041386</v>
+        <v>7041481</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2976,10 +2962,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123235375</v>
+        <v>123231596</v>
       </c>
       <c r="B24" t="n">
-        <v>90983</v>
+        <v>57490</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2992,34 +2978,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585426</v>
+        <v>585465</v>
       </c>
       <c r="R24" t="n">
-        <v>7041283</v>
+        <v>7041291</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3052,6 +3043,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3078,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123232716</v>
+        <v>123232462</v>
       </c>
       <c r="B25" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,38 +3086,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585414</v>
+        <v>585466</v>
       </c>
       <c r="R25" t="n">
-        <v>7041365</v>
+        <v>7041382</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3183,7 +3183,7 @@
         <v>123236358</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>91337</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123233683</v>
+        <v>123232716</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,39 +1822,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585497</v>
+        <v>585414</v>
       </c>
       <c r="R13" t="n">
-        <v>7041338</v>
+        <v>7041365</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1887,11 +1882,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,7 +1911,7 @@
         <v>123234354</v>
       </c>
       <c r="B14" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123235320</v>
+        <v>123231596</v>
       </c>
       <c r="B15" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,16 +2026,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,7 +2046,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2065,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585455</v>
+        <v>585465</v>
       </c>
       <c r="R15" t="n">
-        <v>7041321</v>
+        <v>7041291</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2101,6 +2091,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,10 +2122,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123235375</v>
+        <v>123236138</v>
       </c>
       <c r="B16" t="n">
-        <v>90988</v>
+        <v>91277</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,21 +2138,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585426</v>
+        <v>585273</v>
       </c>
       <c r="R16" t="n">
-        <v>7041283</v>
+        <v>7041240</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2229,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123232716</v>
+        <v>123232752</v>
       </c>
       <c r="B17" t="n">
-        <v>90988</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,21 +2240,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585414</v>
+        <v>585409</v>
       </c>
       <c r="R17" t="n">
-        <v>7041365</v>
+        <v>7041371</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2331,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236138</v>
+        <v>123234392</v>
       </c>
       <c r="B18" t="n">
-        <v>91275</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,21 +2342,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585273</v>
+        <v>585531</v>
       </c>
       <c r="R18" t="n">
-        <v>7041240</v>
+        <v>7041481</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2433,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123231973</v>
+        <v>123235320</v>
       </c>
       <c r="B19" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,16 +2444,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2469,7 +2464,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2478,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585476</v>
+        <v>585455</v>
       </c>
       <c r="R19" t="n">
-        <v>7041349</v>
+        <v>7041321</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2514,11 +2509,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123232328</v>
+        <v>123232462</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,7 +2570,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2589,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585493</v>
+        <v>585466</v>
       </c>
       <c r="R20" t="n">
-        <v>7041342</v>
+        <v>7041382</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2625,11 +2615,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,7 +2644,7 @@
         <v>123233556</v>
       </c>
       <c r="B21" t="n">
-        <v>90984</v>
+        <v>90986</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2758,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123232752</v>
+        <v>123235375</v>
       </c>
       <c r="B22" t="n">
-        <v>79867</v>
+        <v>90990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,21 +2759,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2798,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585409</v>
+        <v>585426</v>
       </c>
       <c r="R22" t="n">
-        <v>7041371</v>
+        <v>7041283</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2860,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123234392</v>
+        <v>123233683</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2876,34 +2861,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585531</v>
+        <v>585497</v>
       </c>
       <c r="R23" t="n">
-        <v>7041481</v>
+        <v>7041338</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2936,6 +2926,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, torrgran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2962,10 +2957,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123231596</v>
+        <v>123232328</v>
       </c>
       <c r="B24" t="n">
-        <v>57490</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2974,31 +2969,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3007,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585465</v>
+        <v>585493</v>
       </c>
       <c r="R24" t="n">
-        <v>7041291</v>
+        <v>7041342</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3047,7 +3041,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,10 +3068,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123232462</v>
+        <v>123231973</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>57491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3086,30 +3080,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3118,10 +3113,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585466</v>
+        <v>585476</v>
       </c>
       <c r="R25" t="n">
-        <v>7041382</v>
+        <v>7041349</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3154,6 +3149,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,7 +3183,7 @@
         <v>123236358</v>
       </c>
       <c r="B26" t="n">
-        <v>91337</v>
+        <v>91339</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -2224,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123232752</v>
+        <v>123235320</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,34 +2240,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585409</v>
+        <v>585455</v>
       </c>
       <c r="R17" t="n">
-        <v>7041371</v>
+        <v>7041321</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2428,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123235320</v>
+        <v>123232752</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>79869</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,39 +2449,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585455</v>
+        <v>585409</v>
       </c>
       <c r="R19" t="n">
-        <v>7041321</v>
+        <v>7041371</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123231596</v>
+        <v>123236138</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>91277</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,39 +2026,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585465</v>
+        <v>585273</v>
       </c>
       <c r="R15" t="n">
-        <v>7041291</v>
+        <v>7041240</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2091,11 +2086,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236138</v>
+        <v>123231596</v>
       </c>
       <c r="B16" t="n">
-        <v>91277</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,34 +2128,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585273</v>
+        <v>585465</v>
       </c>
       <c r="R16" t="n">
-        <v>7041240</v>
+        <v>7041291</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2198,6 +2193,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235320</v>
+        <v>123232752</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,39 +2240,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585455</v>
+        <v>585409</v>
       </c>
       <c r="R17" t="n">
-        <v>7041321</v>
+        <v>7041371</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2433,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123232752</v>
+        <v>123235320</v>
       </c>
       <c r="B19" t="n">
-        <v>79869</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,34 +2444,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585409</v>
+        <v>585455</v>
       </c>
       <c r="R19" t="n">
-        <v>7041371</v>
+        <v>7041321</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 11577-2025 artfynd.xlsx
+++ b/artfynd/A 11577-2025 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123236138</v>
+        <v>123235320</v>
       </c>
       <c r="B15" t="n">
-        <v>91277</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,34 +2026,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585273</v>
+        <v>585455</v>
       </c>
       <c r="R15" t="n">
-        <v>7041240</v>
+        <v>7041321</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2112,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123231596</v>
+        <v>123235375</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,39 +2133,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585465</v>
+        <v>585426</v>
       </c>
       <c r="R16" t="n">
-        <v>7041291</v>
+        <v>7041283</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2193,11 +2193,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123232752</v>
+        <v>123236138</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>91277</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2264,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585409</v>
+        <v>585273</v>
       </c>
       <c r="R17" t="n">
-        <v>7041371</v>
+        <v>7041240</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2326,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123234392</v>
+        <v>123231596</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2342,34 +2337,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585531</v>
+        <v>585465</v>
       </c>
       <c r="R18" t="n">
-        <v>7041481</v>
+        <v>7041291</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2402,6 +2402,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2428,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123235320</v>
+        <v>123232328</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,31 +2445,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2473,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585455</v>
+        <v>585493</v>
       </c>
       <c r="R19" t="n">
-        <v>7041321</v>
+        <v>7041342</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2509,6 +2513,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2538,7 +2547,7 @@
         <v>123232462</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,10 +2650,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123233556</v>
+        <v>123232752</v>
       </c>
       <c r="B21" t="n">
-        <v>90986</v>
+        <v>79869</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2657,21 +2666,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2681,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585476</v>
+        <v>585409</v>
       </c>
       <c r="R21" t="n">
-        <v>7041386</v>
+        <v>7041371</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2743,10 +2752,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123235375</v>
+        <v>123231973</v>
       </c>
       <c r="B22" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2759,34 +2768,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585426</v>
+        <v>585476</v>
       </c>
       <c r="R22" t="n">
-        <v>7041283</v>
+        <v>7041349</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2819,6 +2833,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123232328</v>
+        <v>123234392</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,42 +2988,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585493</v>
+        <v>585531</v>
       </c>
       <c r="R24" t="n">
-        <v>7041342</v>
+        <v>7041481</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3037,11 +3052,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Delvis snötäckt mark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3068,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123231973</v>
+        <v>123233556</v>
       </c>
       <c r="B25" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,29 +3094,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
@@ -3116,7 +3121,7 @@
         <v>585476</v>
       </c>
       <c r="R25" t="n">
-        <v>7041349</v>
+        <v>7041386</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3149,11 +3154,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
